--- a/packages/knowledge-seed/deliverable-shells/estimate-summary-v1.xlsx
+++ b/packages/knowledge-seed/deliverable-shells/estimate-summary-v1.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -96,6 +96,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -647,6 +648,20 @@
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>«bind»</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Estimate overview (AI-written)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>«bind»</t>
         </is>
